--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486743_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486743_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>P. ROBLES LLANOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7837</v>
+        <v>5.9078</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7542</v>
+        <v>3.7987</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0295</v>
+        <v>2.1091</v>
       </c>
       <c r="G2" t="n">
-        <v>3.93</v>
+        <v>4.6635</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7862</v>
+        <v>2.0275</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1439</v>
+        <v>2.6359</v>
       </c>
       <c r="J2" t="n">
-        <v>4.469</v>
+        <v>4.168</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6145</v>
+        <v>1.6835</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8545</v>
+        <v>2.4845</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.539</v>
+        <v>0.4955</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8283</v>
+        <v>0.344</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2893</v>
+        <v>0.1514</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1931</v>
+        <v>1.1585</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1239</v>
+        <v>3.0892</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4329</v>
+        <v>-0.8136</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3165</v>
+        <v>-0.5657</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1164</v>
+        <v>-0.2479</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2277</v>
+        <v>0.8995</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8995</v>
+        <v>2.1271</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3282</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. ROBLES LLANOS</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3036</v>
+        <v>5.8888</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5918</v>
+        <v>4.3063</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7118</v>
+        <v>1.5825</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6635</v>
+        <v>3.93</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0275</v>
+        <v>2.7862</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6359</v>
+        <v>1.1439</v>
       </c>
       <c r="J3" t="n">
-        <v>4.168</v>
+        <v>4.469</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6835</v>
+        <v>3.6145</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4845</v>
+        <v>0.8545</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4955</v>
+        <v>-0.539</v>
       </c>
       <c r="N3" t="n">
-        <v>0.344</v>
+        <v>-0.8283</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1514</v>
+        <v>0.2893</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1585</v>
+        <v>0.1931</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0892</v>
+        <v>2.1239</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4178</v>
+        <v>0.538</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7725</v>
+        <v>0.8686</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6452</v>
+        <v>-0.3306</v>
       </c>
       <c r="V3" t="n">
+        <v>1.2277</v>
+      </c>
+      <c r="W3" t="n">
         <v>0.8995</v>
       </c>
-      <c r="W3" t="n">
-        <v>2.1271</v>
-      </c>
       <c r="X3" t="n">
-        <v>-1.2277</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1373</v>
+        <v>5.0806</v>
       </c>
       <c r="E4" t="n">
-        <v>5.116</v>
+        <v>5.7365</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9787</v>
+        <v>-0.6559</v>
       </c>
       <c r="G4" t="n">
         <v>4.2709</v>
@@ -766,13 +766,13 @@
         <v>0.5792</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9984</v>
+        <v>-0.0551</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3863</v>
+        <v>0.2343</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6122</v>
+        <v>-0.2894</v>
       </c>
       <c r="V4" t="n">
         <v>0.2856</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0382</v>
+        <v>3.6286</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8639</v>
+        <v>3.5536</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1743</v>
+        <v>0.075</v>
       </c>
       <c r="G5" t="n">
         <v>1.6337</v>
@@ -844,13 +844,13 @@
         <v>1.7377</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5131</v>
+        <v>0.1035</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9927</v>
+        <v>0.6824</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4796</v>
+        <v>-0.5789</v>
       </c>
       <c r="V5" t="n">
         <v>2.0845</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7777</v>
+        <v>3.2826</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1996</v>
+        <v>0.4064</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5782</v>
+        <v>2.8761</v>
       </c>
       <c r="G6" t="n">
         <v>0.1514</v>
@@ -922,13 +922,13 @@
         <v>2.1239</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9875</v>
+        <v>-0.4826</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8277</v>
+        <v>-0.6209</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1597</v>
+        <v>0.1383</v>
       </c>
       <c r="V6" t="n">
         <v>2.4554</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5162</v>
+        <v>2.9564</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1077</v>
+        <v>3.847</v>
       </c>
       <c r="F7" t="n">
-        <v>2.624</v>
+        <v>-0.8905999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7751</v>
+        <v>3.7163</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0894</v>
+        <v>2.7104</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3143</v>
+        <v>1.006</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2247</v>
+        <v>4.1173</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0212</v>
+        <v>3.2627</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2035</v>
+        <v>0.8545</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4495</v>
+        <v>-0.4009</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0682</v>
+        <v>-0.5524</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5178</v>
+        <v>0.1514</v>
       </c>
       <c r="P7" t="n">
+        <v>0.9654</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.9654</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-2.8962</v>
       </c>
       <c r="R7" t="n">
         <v>1.9308</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7491</v>
+        <v>-0.455</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.1239</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1427</v>
+        <v>-0.5789</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0426</v>
+        <v>-1.2703</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0426</v>
+        <v>0.5712</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1868</v>
+        <v>2.2625</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2265</v>
+        <v>0.8361</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0396</v>
+        <v>1.4264</v>
       </c>
       <c r="G8" t="n">
-        <v>3.7163</v>
+        <v>0.738</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7104</v>
+        <v>2.2346</v>
       </c>
       <c r="I8" t="n">
-        <v>1.006</v>
+        <v>-1.4966</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1173</v>
+        <v>0.9809</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2627</v>
+        <v>2.2355</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8545</v>
+        <v>-1.2546</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4009</v>
+        <v>-0.2429</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5524</v>
+        <v>-0.0009</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1514</v>
+        <v>-0.242</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9654</v>
+        <v>1.1585</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9308</v>
+        <v>2.1239</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2246</v>
+        <v>-0.8617</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4966</v>
+        <v>-0.4071</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7279</v>
+        <v>-0.4546</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2703</v>
+        <v>1.2277</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5712</v>
+        <v>1.2277</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6791</v>
+        <v>1.1749</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5259</v>
+        <v>-0.4089</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1532</v>
+        <v>1.5838</v>
       </c>
       <c r="G9" t="n">
-        <v>0.738</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2346</v>
+        <v>-0.5587</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4966</v>
+        <v>1.4603</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9809</v>
+        <v>1.0199</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2355</v>
+        <v>-0.2823</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2546</v>
+        <v>1.3022</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2429</v>
+        <v>-0.1182</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0009</v>
+        <v>-0.2764</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.242</v>
+        <v>0.1582</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1585</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1239</v>
+        <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4451</v>
+        <v>-0.055</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7174</v>
+        <v>-0.0692</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7278</v>
+        <v>0.0142</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2277</v>
+        <v>0.3282</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2277</v>
+        <v>0.5712</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.243</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6549</v>
+        <v>1.1466</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.202</v>
+        <v>-0.8317</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8569</v>
+        <v>1.9783</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9016999999999999</v>
+        <v>1.7751</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5587</v>
+        <v>2.0894</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4603</v>
+        <v>-0.3143</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0199</v>
+        <v>2.2247</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2823</v>
+        <v>2.0212</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3022</v>
+        <v>0.2035</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1182</v>
+        <v>-0.4495</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2764</v>
+        <v>0.0682</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1582</v>
+        <v>-0.5178</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R10" t="n">
         <v>1.9308</v>
       </c>
       <c r="S10" t="n">
-        <v>0.425</v>
+        <v>0.3795</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1377</v>
+        <v>-0.1175</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2874</v>
+        <v>0.4971</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3282</v>
+        <v>-0.0426</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5712</v>
+        <v>-0.0426</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.351</v>
+        <v>0.8929</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2207</v>
+        <v>1.7379</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8698</v>
+        <v>-0.845</v>
       </c>
       <c r="G11" t="n">
         <v>2.9092</v>
@@ -1312,13 +1312,13 @@
         <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5349</v>
+        <v>0.007</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2759</v>
+        <v>0.2412</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.259</v>
+        <v>-0.2342</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2856</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2057</v>
+        <v>0.0012</v>
       </c>
       <c r="E12" t="n">
-        <v>0.318</v>
+        <v>0.5249</v>
       </c>
       <c r="F12" t="n">
         <v>-0.5237000000000001</v>
@@ -1390,10 +1390,10 @@
         <v>1.5446</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.3723</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4415</v>
+        <v>-0.2346</v>
       </c>
       <c r="U12" t="n">
         <v>-0.1377</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>32.2228</v>
+        <v>32.2229</v>
       </c>
       <c r="E13" t="n">
-        <v>23.5069</v>
+        <v>23.50679999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>8.716099999999999</v>
+        <v>8.716000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>25.0319</v>
@@ -1450,7 +1450,7 @@
         <v>15.4859</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.9425</v>
+        <v>-4.942500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>-3.8003</v>
@@ -1468,16 +1468,16 @@
         <v>20.2733</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.067299999999999</v>
+        <v>-2.0673</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1354000000000004</v>
+        <v>0.1354000000000002</v>
       </c>
       <c r="U13" t="n">
         <v>-2.2026</v>
       </c>
       <c r="V13" t="n">
-        <v>5.3968</v>
+        <v>5.396800000000001</v>
       </c>
       <c r="W13" t="n">
         <v>9.8087</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6415</v>
+        <v>0.7449</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6415</v>
+        <v>0.7449</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1546,10 +1546,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>0.1034</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>0.1034</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.368</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4274</v>
+        <v>0.1172</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0594</v>
+        <v>-0.0346</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0897</v>
@@ -1624,13 +1624,13 @@
         <v>0.1931</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4578</v>
+        <v>0.1723</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.2688</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1213</v>
+        <v>-0.0965</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1636</v>
+        <v>-0.151</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5698</v>
+        <v>1.7766</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4061</v>
+        <v>-1.9276</v>
       </c>
       <c r="G16" t="n">
         <v>-2.0678</v>
@@ -1702,13 +1702,13 @@
         <v>2.7031</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1971</v>
+        <v>0.8825</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0269</v>
+        <v>0.2338</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1702</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>2.1928</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0211</v>
+        <v>-0.7108</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2563</v>
+        <v>2.5666</v>
       </c>
       <c r="F17" t="n">
         <v>-3.2774</v>
@@ -1780,10 +1780,10 @@
         <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3311</v>
+        <v>-0.0208</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0825</v>
+        <v>0.3927</v>
       </c>
       <c r="U17" t="n">
         <v>-0.4136</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MARTÍNEZ LAGO</t>
+          <t>D. MARTINEZ DE LA SERNA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2153</v>
+        <v>-2.1034</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0375</v>
+        <v>-1.8934</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1777</v>
+        <v>-0.21</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.3602</v>
+        <v>-0.5145</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7929</v>
+        <v>-1.0345</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.5673</v>
+        <v>0.5199</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5665</v>
+        <v>-0.0384</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3799</v>
+        <v>-0.6895</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9464</v>
+        <v>0.6511</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.7937</v>
+        <v>-0.4761</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1728</v>
+        <v>-0.345</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6209</v>
+        <v>-0.1311</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5792</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1585</v>
+        <v>-1.9308</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7377</v>
+        <v>0.3862</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5427</v>
+        <v>0.2413</v>
       </c>
       <c r="T18" t="n">
-        <v>2.73</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1873</v>
+        <v>0.1655</v>
       </c>
       <c r="V18" t="n">
-        <v>0.023</v>
+        <v>-0.2856</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0426</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MARTINEZ DE LA SERNA</t>
+          <t>A. MARTÍNEZ LAGO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3062</v>
+        <v>-2.8411</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9968</v>
+        <v>-1.5889</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3093</v>
+        <v>-1.2522</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5145</v>
+        <v>-4.3602</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0345</v>
+        <v>-0.7929</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5199</v>
+        <v>-3.5673</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0384</v>
+        <v>-1.5665</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6895</v>
+        <v>0.3799</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6511</v>
+        <v>-1.9464</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4761</v>
+        <v>-2.7937</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.345</v>
+        <v>-1.1728</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1311</v>
+        <v>-1.6209</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5446</v>
+        <v>0.5792</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9308</v>
+        <v>-1.1585</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3862</v>
+        <v>1.7377</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0386</v>
+        <v>0.9169</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0277</v>
+        <v>1.1787</v>
       </c>
       <c r="U19" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.2618</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2856</v>
+        <v>0.023</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.0426</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2856</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. VALVERDE SASTRE</t>
+          <t>J. BECERRA ORDOÑEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.326</v>
+        <v>-3.426</v>
       </c>
       <c r="E20" t="n">
-        <v>0.137</v>
+        <v>-1.388</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.463</v>
+        <v>-2.038</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9942</v>
+        <v>-2.1678</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4064</v>
+        <v>-0.3864</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5878</v>
+        <v>-1.7814</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.359</v>
+        <v>-0.4706</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4404</v>
+        <v>0.0968</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0814</v>
+        <v>-0.5674</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6352</v>
+        <v>-1.6972</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9661</v>
+        <v>-0.4832</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6692</v>
+        <v>-1.214</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1585</v>
+        <v>0.3862</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1585</v>
+        <v>1.5446</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0774</v>
+        <v>-0.1311</v>
       </c>
       <c r="T20" t="n">
-        <v>0.496</v>
+        <v>0.2411</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5735</v>
+        <v>-0.3722</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4128</v>
+        <v>-1.5133</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4128</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BECERRA ORDOÑEZ</t>
+          <t>J. VALVERDE SASTRE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5543</v>
+        <v>-3.6692</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4914</v>
+        <v>-0.3801</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0629</v>
+        <v>-3.2892</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1678</v>
+        <v>-1.9942</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3864</v>
+        <v>-1.4064</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7814</v>
+        <v>-0.5878</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4706</v>
+        <v>-0.359</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0968</v>
+        <v>-0.4404</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5674</v>
+        <v>0.0814</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6972</v>
+        <v>-1.6352</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4832</v>
+        <v>-0.9661</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.214</v>
+        <v>-0.6692</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5446</v>
+        <v>1.1585</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2594</v>
+        <v>-0.4207</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1377</v>
+        <v>-0.0211</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.397</v>
+        <v>-0.3997</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5133</v>
+        <v>-2.4128</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5133</v>
+        <v>-2.4128</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. MARTIN LLUNA</t>
+          <t>A. TORRES MUNICIO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4288</v>
+        <v>-4.3451</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2133</v>
+        <v>-3.3385</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.6421</v>
+        <v>-1.0066</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.2937</v>
+        <v>-5.6563</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.6065</v>
+        <v>-2.8825</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6873</v>
+        <v>-2.7737</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4799</v>
+        <v>-4.3659</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.985</v>
+        <v>-2.2613</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4649</v>
+        <v>-2.1046</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.7736</v>
+        <v>-1.2904</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.6214</v>
+        <v>-0.6212</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.1522</v>
+        <v>-0.6692</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3515</v>
+        <v>1.9308</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9654</v>
+        <v>-0.1931</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3169</v>
+        <v>2.1239</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6176</v>
+        <v>-0.0484</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4132</v>
+        <v>-0.0073</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2044</v>
+        <v>-0.0411</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1041</v>
+        <v>-0.5712</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3897</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. TORRES MUNICIO</t>
+          <t>D. MARTIN LLUNA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0028</v>
+        <v>-4.4328</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2693</v>
+        <v>0.1099</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-4.5428</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.6563</v>
+        <v>-4.2937</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8825</v>
+        <v>-3.6065</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.7737</v>
+        <v>-0.6873</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.3659</v>
+        <v>0.4799</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.2613</v>
+        <v>-0.985</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.1046</v>
+        <v>1.4649</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2904</v>
+        <v>-4.7736</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6212</v>
+        <v>-2.6214</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6692</v>
+        <v>-2.1522</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9308</v>
+        <v>1.3515</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1931</v>
+        <v>-0.9654</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1239</v>
+        <v>2.3169</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.706</v>
+        <v>0.6135</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9381</v>
+        <v>0.3098</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2321</v>
+        <v>0.3037</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5712</v>
+        <v>-2.1041</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2277</v>
+        <v>0.2856</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7989</v>
+        <v>-2.3897</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LAHOZ</t>
+          <t>D. AVILA MERCADO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.0188</v>
+        <v>-5.65</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4095</v>
+        <v>-3.0328</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.6093</v>
+        <v>-2.6172</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.34</v>
+        <v>-1.0625</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0825</v>
+        <v>-2.4279</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.2576</v>
+        <v>1.3654</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7321</v>
+        <v>3.9803</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6422</v>
+        <v>0.1936</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3744</v>
+        <v>3.7867</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.6079</v>
+        <v>-5.0428</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.7247</v>
+        <v>-2.6216</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.8832</v>
+        <v>-2.4212</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-5.7923</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9654</v>
+        <v>-7.7231</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9654</v>
+        <v>1.9308</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4085</v>
+        <v>-0.1311</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0555</v>
+        <v>-0.5177</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3529</v>
+        <v>0.3866</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2703</v>
+        <v>1.336</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.6565</v>
+        <v>1.2277</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6138</v>
+        <v>0.1083</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. AVILA MERCADO</t>
+          <t>J. JIMENEZ LAHOZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.523</v>
+        <v>-5.7208</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7568</v>
+        <v>-2.4095</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7662</v>
+        <v>-3.3113</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.0625</v>
+        <v>-4.34</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.4279</v>
+        <v>-1.0825</v>
       </c>
       <c r="I25" t="n">
-        <v>1.3654</v>
+        <v>-3.2576</v>
       </c>
       <c r="J25" t="n">
-        <v>3.9803</v>
+        <v>-0.7321</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1936</v>
+        <v>0.6422</v>
       </c>
       <c r="L25" t="n">
-        <v>3.7867</v>
+        <v>-1.3744</v>
       </c>
       <c r="M25" t="n">
-        <v>-5.0428</v>
+        <v>-3.6079</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.6216</v>
+        <v>-1.7247</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.4212</v>
+        <v>-1.8832</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.7923</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-7.7231</v>
+        <v>-0.9654</v>
       </c>
       <c r="R25" t="n">
-        <v>1.9308</v>
+        <v>0.9654</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0041</v>
+        <v>-0.1105</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2417</v>
+        <v>-0.0555</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2376</v>
+        <v>-0.0549</v>
       </c>
       <c r="V25" t="n">
-        <v>1.336</v>
+        <v>-1.2703</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2277</v>
+        <v>-0.6565</v>
       </c>
       <c r="X25" t="n">
-        <v>0.1083</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-32.2232</v>
+        <v>-32.2227</v>
       </c>
       <c r="E26" t="n">
         <v>-8.715999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-23.5068</v>
+        <v>-23.5069</v>
       </c>
       <c r="G26" t="n">
         <v>-25.0317</v>
@@ -2458,10 +2458,10 @@
         <v>4.942600000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>3.8004</v>
+        <v>3.800400000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>1.142100000000001</v>
+        <v>1.1421</v>
       </c>
       <c r="M26" t="n">
         <v>-29.9742</v>
@@ -2482,13 +2482,13 @@
         <v>16.4117</v>
       </c>
       <c r="S26" t="n">
-        <v>2.067300000000001</v>
+        <v>2.0673</v>
       </c>
       <c r="T26" t="n">
-        <v>2.2024</v>
+        <v>2.202500000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1351000000000001</v>
+        <v>-0.1352999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-5.396699999999999</v>
